--- a/artfynd/A 29157-2023 artfynd.xlsx
+++ b/artfynd/A 29157-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29157-2023 artfynd.xlsx
+++ b/artfynd/A 29157-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113033850</v>
+        <v>113033870</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,13 +711,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388163</v>
+        <v>388212</v>
       </c>
       <c r="R2" t="n">
-        <v>6243071</v>
+        <v>6243150</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bengt  Bengtsson </t>
+          <t>Bengt  Bengtsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bengt  Bengtsson </t>
+          <t>Bengt  Bengtsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113033870</v>
+        <v>113033850</v>
       </c>
       <c r="B3" t="n">
-        <v>56908</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,13 +809,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388212</v>
+        <v>388163</v>
       </c>
       <c r="R3" t="n">
-        <v>6243150</v>
+        <v>6243071</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +859,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bengt  Bengtsson </t>
+          <t>Bengt  Bengtsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bengt  Bengtsson </t>
+          <t>Bengt  Bengtsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 29157-2023 artfynd.xlsx
+++ b/artfynd/A 29157-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113033870</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,8 +878,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113033850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>